--- a/out/M04_hotel_stay_experience/agent3/agent3_test_cases_with_paths.xlsx
+++ b/out/M04_hotel_stay_experience/agent3/agent3_test_cases_with_paths.xlsx
@@ -906,7 +906,7 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>11 test(s): TC-FT46, TC-FT47, TC-FT48, TC-FT49, TC-FT50, TC-FT51 ...</t>
+          <t>9 test(s): TC-FT43, TC-FT44, TC-FT45, TC-FT46, TC-FT57, TC-FT58 ...</t>
         </is>
       </c>
       <c r="Q7" s="8" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>15 test(s): TC-FT31, TC-FT32, TC-FT33, TC-FT34, TC-FT35, TC-FT36 ...</t>
+          <t>12 test(s): TC-FT31, TC-FT32, TC-FT33, TC-FT34, TC-FT35, TC-FT36 ...</t>
         </is>
       </c>
       <c r="Q10" s="8" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE85"/>
+  <dimension ref="A1:AE80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7575,12 +7575,12 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>3. Dependency / Piping</t>
+          <t>9. Rule Interaction</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
@@ -7590,17 +7590,17 @@
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>Q8 quotes the answer given at Q7</t>
+          <t>Q8 is shown and reflects its dependency on Q7 at the same time</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>Prove Q8's wording is built from the answer given at Q7, so the respondent is only asked about what they actually chose.</t>
+          <t>Prove Q8 is shown by its display rule and simultaneously reflects its dependency on Q7. Each mechanism can be correct alone and still disagree together.</t>
         </is>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>A question that quotes the wrong earlier answer reads as a different question entirely to the respondent.</t>
+          <t>Individually correct rules can combine into behaviour neither one describes on its own.</t>
         </is>
       </c>
       <c r="K44" s="6" t="inlineStr">
@@ -7666,7 +7666,8 @@
       </c>
       <c r="W44" s="6" t="inlineStr">
         <is>
-          <t>1. Q8's wording includes: Room cleanliness</t>
+          <t>1. Q8 is on screen
+2. Q8's wording includes: Room cleanliness</t>
         </is>
       </c>
       <c r="X44" s="6" t="inlineStr">
@@ -7717,7 +7718,7 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
@@ -7732,12 +7733,12 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>9. Rule Interaction</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
@@ -7747,27 +7748,27 @@
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>Q8 is shown and reflects its dependency on Q7 at the same time</t>
+          <t>Q9 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>Prove Q8 is shown by its display rule and simultaneously reflects its dependency on Q7. Each mechanism can be correct alone and still disagree together.</t>
+          <t>Prove that answering Q9 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>Individually correct rules can combine into behaviour neither one describes on its own.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L45" s="6" t="inlineStr">
         <is>
-          <t>Travel path P06 (Completing respondent — Q7=Billing problem; Q9=No) as far as Q8.</t>
+          <t>Travel path P06 (Completing respondent — Q7=Billing problem; Q9=No) as far as Q9.</t>
         </is>
       </c>
       <c r="M45" s="6" t="inlineStr">
@@ -7777,8 +7778,8 @@
       </c>
       <c r="N45" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness
-then: At Q8, choose “Room cleanliness”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O45" s="6" t="inlineStr">
@@ -7788,12 +7789,12 @@
       </c>
       <c r="P45" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
+          <t>Every answer before Q9 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q9 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q45" s="6" t="inlineStr">
         <is>
-          <t>At Q8, choose “Room cleanliness”, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
@@ -7823,8 +7824,8 @@
       </c>
       <c r="W45" s="6" t="inlineStr">
         <is>
-          <t>1. Q8 is on screen
-2. Q8's wording includes: Room cleanliness</t>
+          <t>1. Q9 is on screen
+2. the next question shown is Q10</t>
         </is>
       </c>
       <c r="X45" s="6" t="inlineStr">
@@ -7839,13 +7840,12 @@
       </c>
       <c r="Z45" s="6" t="inlineStr">
         <is>
-          <t>Q8 | Which problem had the greatest impact? | single | Room cleanliness; Noise; Check-in delay; Wi-Fi issue; Billing problem | Show if: Q7 contains any problem
-Show only options selected at Q7.</t>
+          <t>Q9 | Was the main problem resolved? | single | Yes, fully; Yes, partly; No | Show if: Q7 contains any problem</t>
         </is>
       </c>
       <c r="AA45" s="6" t="inlineStr">
         <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
+          <t>Model-inferred. The questionnaire wrote this as prose rather than in a table, so Agent 1 read it with a model and raised it for sign-off. Confirm before relying on this test.</t>
         </is>
       </c>
       <c r="AB45" s="10" t="inlineStr">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="AD45" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE45" s="6" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>Q9 accepts a normal answer and the survey moves on</t>
+          <t>Q9 is shown when its condition is met</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q9 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q9 IS shown when its display rule is satisfied. The rule is: Q7 contains any problem</t>
         </is>
       </c>
       <c r="J46" s="6" t="inlineStr">
@@ -7935,8 +7935,8 @@
       </c>
       <c r="N46" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness
+then: At Q9, choose “Yes, fully”, then submit.</t>
         </is>
       </c>
       <c r="O46" s="6" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="Q46" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q9, choose “Yes, fully”, then submit.</t>
         </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
@@ -7981,8 +7981,7 @@
       </c>
       <c r="W46" s="6" t="inlineStr">
         <is>
-          <t>1. Q9 is on screen
-2. the next question shown is Q10</t>
+          <t>1. Q9 is on screen</t>
         </is>
       </c>
       <c r="X46" s="6" t="inlineStr">
@@ -7997,7 +7996,8 @@
       </c>
       <c r="Z46" s="6" t="inlineStr">
         <is>
-          <t>Q9 | Was the main problem resolved? | single | Yes, fully; Yes, partly; No | Show if: Q7 contains any problem</t>
+          <t>Q9 | Was the main problem resolved? | single | Yes, fully; Yes, partly; No | Show if: Q7 contains any problem
+Rules exercised: R5</t>
         </is>
       </c>
       <c r="AA46" s="6" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="AD46" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE46" s="6" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>Q9 is shown when its condition is met</t>
+          <t>Q9 is not shown when its condition is not met</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>Prove Q9 IS shown when its display rule is satisfied. The rule is: Q7 contains any problem</t>
+          <t>Prove Q9 is NOT shown when its display rule is not satisfied. The rule is: Q7 contains any problem</t>
         </is>
       </c>
       <c r="J47" s="6" t="inlineStr">
@@ -8092,13 +8092,13 @@
       </c>
       <c r="N47" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness
-then: At Q9, choose “Yes, fully”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = None of these
+then: After submitting Q7, look for Q9 on the next page. Do not answer it.</t>
         </is>
       </c>
       <c r="O47" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>VALID_TYPICAL (the branch that hides the question)</t>
         </is>
       </c>
       <c r="P47" s="6" t="inlineStr">
@@ -8108,17 +8108,17 @@
       </c>
       <c r="Q47" s="6" t="inlineStr">
         <is>
-          <t>At Q9, choose “Yes, fully”, then submit.</t>
+          <t>After submitting Q7, look for Q9 on the next page. Do not answer it.</t>
         </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S47" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T47" s="6" t="inlineStr">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="U47" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q8, Q9, Q10</t>
         </is>
       </c>
       <c r="V47" s="6" t="inlineStr">
@@ -8138,7 +8138,8 @@
       </c>
       <c r="W47" s="6" t="inlineStr">
         <is>
-          <t>1. Q9 is on screen</t>
+          <t>1. Q9 is NOT on screen
+2. the respondent carries on rather than being screened out or finished</t>
         </is>
       </c>
       <c r="X47" s="6" t="inlineStr">
@@ -8174,12 +8175,12 @@
       </c>
       <c r="AD47" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove why the question was absent beyond the display rule; the check confirms the respondent was still travelling and had not been screened out. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE47" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: multi_equality</t>
+          <t>Leans on an unconfirmed reading: multi_equality, rule_precedence</t>
         </is>
       </c>
     </row>
@@ -8209,7 +8210,7 @@
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
@@ -8219,12 +8220,12 @@
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>Q9 is not shown when its condition is not met</t>
+          <t>R8 jumps forward when its condition is met</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>Prove Q9 is NOT shown when its display rule is not satisfied. The rule is: Q7 contains any problem</t>
+          <t>Prove R8 jumps to Q11. The rule is: Q9 == 'No'</t>
         </is>
       </c>
       <c r="J48" s="6" t="inlineStr">
@@ -8249,13 +8250,13 @@
       </c>
       <c r="N48" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = None of these
-then: After submitting Q7, look for Q9 on the next page. Do not answer it.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness
+then: At Q9, choose “No”, then submit.</t>
         </is>
       </c>
       <c r="O48" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL (the branch that hides the question)</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P48" s="6" t="inlineStr">
@@ -8265,17 +8266,17 @@
       </c>
       <c r="Q48" s="6" t="inlineStr">
         <is>
-          <t>After submitting Q7, look for Q9 on the next page. Do not answer it.</t>
+          <t>At Q9, choose “No”, then submit.</t>
         </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S48" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T48" s="6" t="inlineStr">
@@ -8285,7 +8286,7 @@
       </c>
       <c r="U48" s="6" t="inlineStr">
         <is>
-          <t>Q8, Q9, Q10</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="V48" s="6" t="inlineStr">
@@ -8295,8 +8296,7 @@
       </c>
       <c r="W48" s="6" t="inlineStr">
         <is>
-          <t>1. Q9 is NOT on screen
-2. the respondent carries on rather than being screened out or finished</t>
+          <t>1. the next question shown is Q11</t>
         </is>
       </c>
       <c r="X48" s="6" t="inlineStr">
@@ -8312,12 +8312,12 @@
       <c r="Z48" s="6" t="inlineStr">
         <is>
           <t>Q9 | Was the main problem resolved? | single | Yes, fully; Yes, partly; No | Show if: Q7 contains any problem
-Rules exercised: R5</t>
+Rules exercised: R8</t>
         </is>
       </c>
       <c r="AA48" s="6" t="inlineStr">
         <is>
-          <t>Model-inferred. The questionnaire wrote this as prose rather than in a table, so Agent 1 read it with a model and raised it for sign-off. Confirm before relying on this test.</t>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
       <c r="AB48" s="10" t="inlineStr">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="AD48" s="6" t="inlineStr">
         <is>
-          <t>It does not prove why the question was absent beyond the display rule; the check confirms the respondent was still travelling and had not been screened out. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE48" s="6" t="inlineStr">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
@@ -8377,12 +8377,12 @@
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>R8 jumps forward when its condition is met</t>
+          <t>R8 does not jump when its condition is not met</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>Prove R8 jumps to Q11. The rule is: Q9 == 'No'</t>
+          <t>Prove R8 does not jump and the respondent continues in sequence. The rule is: Q9 == 'No'</t>
         </is>
       </c>
       <c r="J49" s="6" t="inlineStr">
@@ -8408,7 +8408,7 @@
       <c r="N49" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness
-then: At Q9, choose “No”, then submit.</t>
+then: At Q9, choose “Yes, fully”, then submit.</t>
         </is>
       </c>
       <c r="O49" s="6" t="inlineStr">
@@ -8423,17 +8423,17 @@
       </c>
       <c r="Q49" s="6" t="inlineStr">
         <is>
-          <t>At Q9, choose “No”, then submit.</t>
+          <t>At Q9, choose “Yes, fully”, then submit.</t>
         </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S49" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T49" s="6" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="U49" s="6" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V49" s="6" t="inlineStr">
@@ -8453,7 +8453,7 @@
       </c>
       <c r="W49" s="6" t="inlineStr">
         <is>
-          <t>1. the next question shown is Q11</t>
+          <t>1. the next question shown is Q10</t>
         </is>
       </c>
       <c r="X49" s="6" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="AE49" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: multi_equality, rule_precedence</t>
+          <t>Leans on an unconfirmed reading: multi_equality</t>
         </is>
       </c>
     </row>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
@@ -8534,22 +8534,22 @@
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>R8 does not jump when its condition is not met</t>
+          <t>Q9 blocks a blank answer</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>Prove R8 does not jump and the respondent continues in sequence. The rule is: Q9 == 'No'</t>
+          <t>Prove Q9 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K50" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L50" s="6" t="inlineStr">
@@ -8565,12 +8565,12 @@
       <c r="N50" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness
-then: At Q9, choose “Yes, fully”, then submit.</t>
+then: At Q9, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O50" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P50" s="6" t="inlineStr">
@@ -8580,17 +8580,17 @@
       </c>
       <c r="Q50" s="6" t="inlineStr">
         <is>
-          <t>At Q9, choose “Yes, fully”, then submit.</t>
+          <t>At Q9, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9  (refused at Q9; respondent stays put)</t>
         </is>
       </c>
       <c r="S50" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9</t>
         </is>
       </c>
       <c r="T50" s="6" t="inlineStr">
@@ -8600,22 +8600,23 @@
       </c>
       <c r="U50" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="V50" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W50" s="6" t="inlineStr">
         <is>
-          <t>1. the next question shown is Q10</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q9</t>
         </is>
       </c>
       <c r="X50" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y50" s="6" t="inlineStr">
@@ -8625,13 +8626,12 @@
       </c>
       <c r="Z50" s="6" t="inlineStr">
         <is>
-          <t>Q9 | Was the main problem resolved? | single | Yes, fully; Yes, partly; No | Show if: Q7 contains any problem
-Rules exercised: R8</t>
+          <t>Q9 | Was the main problem resolved? | single | Yes, fully; Yes, partly; No | Show if: Q7 contains any problem</t>
         </is>
       </c>
       <c r="AA50" s="6" t="inlineStr">
         <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
+          <t>Model-inferred. The questionnaire wrote this as prose rather than in a table, so Agent 1 read it with a model and raised it for sign-off. Confirm before relying on this test.</t>
         </is>
       </c>
       <c r="AB50" s="10" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="AD50" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE50" s="6" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
@@ -8676,42 +8676,42 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>Q9 blocks a blank answer</t>
+          <t>Q10 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>Prove Q9 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove that answering Q10 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L51" s="6" t="inlineStr">
         <is>
-          <t>Travel path P06 (Completing respondent — Q7=Billing problem; Q9=No) as far as Q9.</t>
+          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as Q10.</t>
         </is>
       </c>
       <c r="M51" s="6" t="inlineStr">
@@ -8721,59 +8721,59 @@
       </c>
       <c r="N51" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness
-then: At Q9, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O51" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P51" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q9 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q9 is the one the claim turns on.</t>
+          <t>Every answer before Q10 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q10 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q51" s="6" t="inlineStr">
         <is>
-          <t>At Q9, select nothing at all, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9  (refused at Q9; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S51" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T51" s="6" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U51" s="6" t="inlineStr">
         <is>
-          <t>Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V51" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W51" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q9</t>
+          <t>1. Q10 is on screen
+2. the next question shown is Q11</t>
         </is>
       </c>
       <c r="X51" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y51" s="6" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="Z51" s="6" t="inlineStr">
         <is>
-          <t>Q9 | Was the main problem resolved? | single | Yes, fully; Yes, partly; No | Show if: Q7 contains any problem</t>
+          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']</t>
         </is>
       </c>
       <c r="AA51" s="6" t="inlineStr">
         <is>
-          <t>Model-inferred. The questionnaire wrote this as prose rather than in a table, so Agent 1 read it with a model and raised it for sign-off. Confirm before relying on this test.</t>
+          <t>Derived by rule from the questionnaire's own tables.</t>
         </is>
       </c>
       <c r="AB51" s="10" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="AD51" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE51" s="6" t="inlineStr">
@@ -8818,7 +8818,7 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
@@ -8833,7 +8833,7 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>3. Dependency / Piping</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
@@ -8843,32 +8843,32 @@
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>Q9 quotes the answer given at Q8</t>
+          <t>Q10 is shown when its condition is met</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>Prove Q9's wording is built from the answer given at Q8, so the respondent is only asked about what they actually chose.</t>
+          <t>Prove Q10 IS shown when its display rule is satisfied. The rule is: Q9 in ['Yes, fully','Yes, partly']</t>
         </is>
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>A question that quotes the wrong earlier answer reads as a different question entirely to the respondent.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K52" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L52" s="6" t="inlineStr">
         <is>
-          <t>Travel path P06 (Completing respondent — Q7=Billing problem; Q9=No) as far as Q9.</t>
+          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as Q10.</t>
         </is>
       </c>
       <c r="M52" s="6" t="inlineStr">
@@ -8878,8 +8878,8 @@
       </c>
       <c r="N52" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness
-then: At Q9, choose “Yes, fully”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully
+then: At Q10, choose “Very poor”, then submit.</t>
         </is>
       </c>
       <c r="O52" s="6" t="inlineStr">
@@ -8889,12 +8889,12 @@
       </c>
       <c r="P52" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q9 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q9 is the one the claim turns on.</t>
+          <t>Every answer before Q10 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q10 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q52" s="6" t="inlineStr">
         <is>
-          <t>At Q9, choose “Yes, fully”, then submit.</t>
+          <t>At Q10, choose “Very poor”, then submit.</t>
         </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="T52" s="6" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U52" s="6" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="W52" s="6" t="inlineStr">
         <is>
-          <t>1. Q9's wording includes: Room cleanliness</t>
+          <t>1. Q10 is on screen</t>
         </is>
       </c>
       <c r="X52" s="6" t="inlineStr">
@@ -8939,12 +8939,13 @@
       </c>
       <c r="Z52" s="6" t="inlineStr">
         <is>
-          <t>Q9 | Was the main problem resolved? | single | Yes, fully; Yes, partly; No | Show if: Q7 contains any problem</t>
+          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']
+Rules exercised: R7</t>
         </is>
       </c>
       <c r="AA52" s="6" t="inlineStr">
         <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
+          <t>Derived by rule from the questionnaire's own tables.</t>
         </is>
       </c>
       <c r="AB52" s="10" t="inlineStr">
@@ -8974,7 +8975,7 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
@@ -8989,42 +8990,42 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>9. Rule Interaction</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>Q9 is shown and reflects its dependency on Q8 at the same time</t>
+          <t>Q10 is not shown when its condition is not met</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>Prove Q9 is shown by its display rule and simultaneously reflects its dependency on Q8. Each mechanism can be correct alone and still disagree together.</t>
+          <t>Prove Q10 is NOT shown when its display rule is not satisfied. The rule is: Q9 in ['Yes, fully','Yes, partly']</t>
         </is>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>Individually correct rules can combine into behaviour neither one describes on its own.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L53" s="6" t="inlineStr">
         <is>
-          <t>Travel path P06 (Completing respondent — Q7=Billing problem; Q9=No) as far as Q9.</t>
+          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as Q10.</t>
         </is>
       </c>
       <c r="M53" s="6" t="inlineStr">
@@ -9034,45 +9035,45 @@
       </c>
       <c r="N53" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness
-then: At Q9, choose “Yes, fully”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = No
+then: After submitting Q9, look for Q10 on the next page. Do not answer it.</t>
         </is>
       </c>
       <c r="O53" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>VALID_TYPICAL (the branch that hides the question)</t>
         </is>
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q9 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q9 is the one the claim turns on.</t>
+          <t>Every answer before Q10 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q10 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
-          <t>At Q9, choose “Yes, fully”, then submit.</t>
+          <t>After submitting Q9, look for Q10 on the next page. Do not answer it.</t>
         </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S53" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T53" s="6" t="inlineStr">
         <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="U53" s="6" t="inlineStr">
+        <is>
           <t>Q10</t>
         </is>
       </c>
-      <c r="U53" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
       <c r="V53" s="6" t="inlineStr">
         <is>
           <t>Each listed question is followed immediately by the next in the sequence.</t>
@@ -9080,8 +9081,8 @@
       </c>
       <c r="W53" s="6" t="inlineStr">
         <is>
-          <t>1. Q9 is on screen
-2. Q9's wording includes: Room cleanliness</t>
+          <t>1. Q10 is NOT on screen
+2. the respondent carries on rather than being screened out or finished</t>
         </is>
       </c>
       <c r="X53" s="6" t="inlineStr">
@@ -9096,12 +9097,13 @@
       </c>
       <c r="Z53" s="6" t="inlineStr">
         <is>
-          <t>Q9 | Was the main problem resolved? | single | Yes, fully; Yes, partly; No | Show if: Q7 contains any problem</t>
+          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']
+Rules exercised: R7</t>
         </is>
       </c>
       <c r="AA53" s="6" t="inlineStr">
         <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
+          <t>Derived by rule from the questionnaire's own tables.</t>
         </is>
       </c>
       <c r="AB53" s="10" t="inlineStr">
@@ -9116,12 +9118,12 @@
       </c>
       <c r="AD53" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove why the question was absent beyond the display rule; the check confirms the respondent was still travelling and had not been screened out. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE53" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: multi_equality</t>
+          <t>Leans on an unconfirmed reading: multi_equality, rule_precedence</t>
         </is>
       </c>
     </row>
@@ -9146,12 +9148,12 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
@@ -9161,22 +9163,22 @@
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>Q10 accepts a normal answer and the survey moves on</t>
+          <t>Q10 blocks a blank answer</t>
         </is>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q10 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q10 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K54" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L54" s="6" t="inlineStr">
@@ -9191,13 +9193,13 @@
       </c>
       <c r="N54" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully
+then: At Q10, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O54" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P54" s="6" t="inlineStr">
@@ -9207,17 +9209,17 @@
       </c>
       <c r="Q54" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q10, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10  (refused at Q10; respondent stays put)</t>
         </is>
       </c>
       <c r="S54" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10</t>
         </is>
       </c>
       <c r="T54" s="6" t="inlineStr">
@@ -9227,23 +9229,23 @@
       </c>
       <c r="U54" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="V54" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W54" s="6" t="inlineStr">
         <is>
-          <t>1. Q10 is on screen
-2. the next question shown is Q11</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q10</t>
         </is>
       </c>
       <c r="X54" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y54" s="6" t="inlineStr">
@@ -9273,7 +9275,7 @@
       </c>
       <c r="AD54" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE54" s="6" t="inlineStr">
@@ -9288,7 +9290,7 @@
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>Q11</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
@@ -9313,17 +9315,17 @@
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>Q10 is shown when its condition is met</t>
+          <t>Q11 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>Prove Q10 IS shown when its display rule is satisfied. The rule is: Q9 in ['Yes, fully','Yes, partly']</t>
+          <t>Prove that answering Q11 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J55" s="6" t="inlineStr">
@@ -9338,7 +9340,7 @@
       </c>
       <c r="L55" s="6" t="inlineStr">
         <is>
-          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as Q10.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q11.</t>
         </is>
       </c>
       <c r="M55" s="6" t="inlineStr">
@@ -9348,8 +9350,8 @@
       </c>
       <c r="N55" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully
-then: At Q10, choose “Very poor”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O55" s="6" t="inlineStr">
@@ -9359,12 +9361,12 @@
       </c>
       <c r="P55" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q10 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q10 is the one the claim turns on.</t>
+          <t>Every answer before Q11 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q11 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q55" s="6" t="inlineStr">
         <is>
-          <t>At Q10, choose “Very poor”, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
@@ -9379,14 +9381,14 @@
       </c>
       <c r="T55" s="6" t="inlineStr">
         <is>
+          <t>Q8, Q9, Q10</t>
+        </is>
+      </c>
+      <c r="U55" s="6" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="U55" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
       <c r="V55" s="6" t="inlineStr">
         <is>
           <t>Each listed question is followed immediately by the next in the sequence.</t>
@@ -9394,7 +9396,8 @@
       </c>
       <c r="W55" s="6" t="inlineStr">
         <is>
-          <t>1. Q10 is on screen</t>
+          <t>1. Q11 is on screen
+2. the next question shown is Q12</t>
         </is>
       </c>
       <c r="X55" s="6" t="inlineStr">
@@ -9409,13 +9412,12 @@
       </c>
       <c r="Z55" s="6" t="inlineStr">
         <is>
-          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']
-Rules exercised: R7</t>
+          <t>Q11 | How likely are you to recommend the provider? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
         </is>
       </c>
       <c r="AA55" s="6" t="inlineStr">
         <is>
-          <t>Derived by rule from the questionnaire's own tables.</t>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
       <c r="AB55" s="10" t="inlineStr">
@@ -9430,7 +9432,7 @@
       </c>
       <c r="AD55" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE55" s="6" t="inlineStr">
@@ -9445,7 +9447,7 @@
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>Q11</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
@@ -9460,7 +9462,7 @@
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
@@ -9470,32 +9472,32 @@
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>Q10 is not shown when its condition is not met</t>
+          <t>Q11 blocks a blank answer</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t>Prove Q10 is NOT shown when its display rule is not satisfied. The rule is: Q9 in ['Yes, fully','Yes, partly']</t>
+          <t>Prove Q11 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K56" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L56" s="6" t="inlineStr">
         <is>
-          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as Q10.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q11.</t>
         </is>
       </c>
       <c r="M56" s="6" t="inlineStr">
@@ -9505,59 +9507,59 @@
       </c>
       <c r="N56" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = No
-then: After submitting Q9, look for Q10 on the next page. Do not answer it.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor
+then: At Q11, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O56" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL (the branch that hides the question)</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P56" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q10 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q10 is the one the claim turns on.</t>
+          <t>Every answer before Q11 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q11 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q56" s="6" t="inlineStr">
         <is>
-          <t>After submitting Q9, look for Q10 on the next page. Do not answer it.</t>
+          <t>At Q11, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11  (refused at Q11; respondent stays put)</t>
         </is>
       </c>
       <c r="S56" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11</t>
         </is>
       </c>
       <c r="T56" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q8, Q9, Q10</t>
         </is>
       </c>
       <c r="U56" s="6" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="V56" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W56" s="6" t="inlineStr">
         <is>
-          <t>1. Q10 is NOT on screen
-2. the respondent carries on rather than being screened out or finished</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q11</t>
         </is>
       </c>
       <c r="X56" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y56" s="6" t="inlineStr">
@@ -9567,13 +9569,12 @@
       </c>
       <c r="Z56" s="6" t="inlineStr">
         <is>
-          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']
-Rules exercised: R7</t>
+          <t>Q11 | How likely are you to recommend the provider? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
         </is>
       </c>
       <c r="AA56" s="6" t="inlineStr">
         <is>
-          <t>Derived by rule from the questionnaire's own tables.</t>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
       <c r="AB56" s="10" t="inlineStr">
@@ -9588,12 +9589,12 @@
       </c>
       <c r="AD56" s="6" t="inlineStr">
         <is>
-          <t>It does not prove why the question was absent beyond the display rule; the check confirms the respondent was still travelling and had not been screened out. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE56" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: multi_equality, rule_precedence</t>
+          <t>Leans on an unconfirmed reading: multi_equality</t>
         </is>
       </c>
     </row>
@@ -9603,7 +9604,7 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>Q12</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
@@ -9618,42 +9619,42 @@
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>Q10 blocks a blank answer</t>
+          <t>Q12 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>Prove Q10 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove that answering Q12 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L57" s="6" t="inlineStr">
         <is>
-          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as Q10.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q12.</t>
         </is>
       </c>
       <c r="M57" s="6" t="inlineStr">
@@ -9663,59 +9664,59 @@
       </c>
       <c r="N57" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully
-then: At Q10, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O57" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P57" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q10 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q10 is the one the claim turns on.</t>
+          <t>Every answer before Q12 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q12 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q57" s="6" t="inlineStr">
         <is>
-          <t>At Q10, select nothing at all, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10  (refused at Q10; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S57" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T57" s="6" t="inlineStr">
         <is>
+          <t>Q8, Q9, Q10</t>
+        </is>
+      </c>
+      <c r="U57" s="6" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="U57" s="6" t="inlineStr">
-        <is>
-          <t>Q11, Q12, Q13, DT2, D1, D2, Q14</t>
-        </is>
-      </c>
       <c r="V57" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W57" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q10</t>
+          <t>1. Q12 is on screen
+2. the next question shown is Q13</t>
         </is>
       </c>
       <c r="X57" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y57" s="6" t="inlineStr">
@@ -9725,12 +9726,12 @@
       </c>
       <c r="Z57" s="6" t="inlineStr">
         <is>
-          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']</t>
+          <t>Q12 | How likely are you to continue using the provider? | single | Definitely not; Probably not; Unsure; Probably; Definitely | Always show</t>
         </is>
       </c>
       <c r="AA57" s="6" t="inlineStr">
         <is>
-          <t>Derived by rule from the questionnaire's own tables.</t>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
       <c r="AB57" s="10" t="inlineStr">
@@ -9745,7 +9746,7 @@
       </c>
       <c r="AD57" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE57" s="6" t="inlineStr">
@@ -9760,7 +9761,7 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>Q12</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
@@ -9775,32 +9776,32 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>3. Dependency / Piping</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>Q10 quotes the answer given at Q9</t>
+          <t>Q12 blocks a blank answer</t>
         </is>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t>Prove Q10's wording is built from the answer given at Q9, so the respondent is only asked about what they actually chose.</t>
+          <t>Prove Q12 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>A question that quotes the wrong earlier answer reads as a different question entirely to the respondent.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K58" s="6" t="inlineStr">
@@ -9810,7 +9811,7 @@
       </c>
       <c r="L58" s="6" t="inlineStr">
         <is>
-          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as Q10.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q12.</t>
         </is>
       </c>
       <c r="M58" s="6" t="inlineStr">
@@ -9820,58 +9821,59 @@
       </c>
       <c r="N58" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully
-then: At Q10, choose “Very poor”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0
+then: At Q12, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O58" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q10 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q10 is the one the claim turns on.</t>
+          <t>Every answer before Q12 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q12 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q58" s="6" t="inlineStr">
         <is>
-          <t>At Q10, choose “Very poor”, then submit.</t>
+          <t>At Q12, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12  (refused at Q12; respondent stays put)</t>
         </is>
       </c>
       <c r="S58" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12</t>
         </is>
       </c>
       <c r="T58" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q8, Q9, Q10</t>
         </is>
       </c>
       <c r="U58" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="V58" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W58" s="6" t="inlineStr">
         <is>
-          <t>1. Q10's wording includes: Yes, fully</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q12</t>
         </is>
       </c>
       <c r="X58" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y58" s="6" t="inlineStr">
@@ -9881,7 +9883,7 @@
       </c>
       <c r="Z58" s="6" t="inlineStr">
         <is>
-          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']</t>
+          <t>Q12 | How likely are you to continue using the provider? | single | Definitely not; Probably not; Unsure; Probably; Definitely | Always show</t>
         </is>
       </c>
       <c r="AA58" s="6" t="inlineStr">
@@ -9901,7 +9903,7 @@
       </c>
       <c r="AD58" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE58" s="6" t="inlineStr">
@@ -9916,7 +9918,7 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>Q13</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
@@ -9931,42 +9933,42 @@
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>9. Rule Interaction</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>Q10 is shown and reflects its dependency on Q9 at the same time</t>
+          <t>Q13 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>Prove Q10 is shown by its display rule and simultaneously reflects its dependency on Q9. Each mechanism can be correct alone and still disagree together.</t>
+          <t>Prove that answering Q13 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>Individually correct rules can combine into behaviour neither one describes on its own.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L59" s="6" t="inlineStr">
         <is>
-          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as Q10.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q13.</t>
         </is>
       </c>
       <c r="M59" s="6" t="inlineStr">
@@ -9976,8 +9978,8 @@
       </c>
       <c r="N59" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully
-then: At Q10, choose “Very poor”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O59" s="6" t="inlineStr">
@@ -9987,12 +9989,12 @@
       </c>
       <c r="P59" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q10 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q10 is the one the claim turns on.</t>
+          <t>Every answer before Q13 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q13 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q59" s="6" t="inlineStr">
         <is>
-          <t>At Q10, choose “Very poor”, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
@@ -10007,14 +10009,14 @@
       </c>
       <c r="T59" s="6" t="inlineStr">
         <is>
+          <t>Q8, Q9, Q10</t>
+        </is>
+      </c>
+      <c r="U59" s="6" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="U59" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
       <c r="V59" s="6" t="inlineStr">
         <is>
           <t>Each listed question is followed immediately by the next in the sequence.</t>
@@ -10022,8 +10024,8 @@
       </c>
       <c r="W59" s="6" t="inlineStr">
         <is>
-          <t>1. Q10 is on screen
-2. Q10's wording includes: Yes, fully</t>
+          <t>1. Q13 is on screen
+2. the next question shown is DT2</t>
         </is>
       </c>
       <c r="X59" s="6" t="inlineStr">
@@ -10038,7 +10040,7 @@
       </c>
       <c r="Z59" s="6" t="inlineStr">
         <is>
-          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']</t>
+          <t>Q13 | Which improvement would have the greatest value? | single | Lower cost; Faster service; Clearer information; Better staff support; Improved digital experience | Randomize</t>
         </is>
       </c>
       <c r="AA59" s="6" t="inlineStr">
@@ -10058,7 +10060,7 @@
       </c>
       <c r="AD59" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE59" s="6" t="inlineStr">
@@ -10073,7 +10075,7 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>Q11</t>
+          <t>Q13</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
@@ -10088,12 +10090,12 @@
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
@@ -10103,27 +10105,27 @@
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>Q11 accepts a normal answer and the survey moves on</t>
+          <t>Q13 blocks a blank answer</t>
         </is>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q11 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q13 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K60" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L60" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q11.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q13.</t>
         </is>
       </c>
       <c r="M60" s="6" t="inlineStr">
@@ -10133,33 +10135,33 @@
       </c>
       <c r="N60" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not
+then: At Q13, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O60" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P60" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q11 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q11 is the one the claim turns on.</t>
+          <t>Every answer before Q13 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q13 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q60" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q13, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13  (refused at Q13; respondent stays put)</t>
         </is>
       </c>
       <c r="S60" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13</t>
         </is>
       </c>
       <c r="T60" s="6" t="inlineStr">
@@ -10169,23 +10171,23 @@
       </c>
       <c r="U60" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="V60" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W60" s="6" t="inlineStr">
         <is>
-          <t>1. Q11 is on screen
-2. the next question shown is Q12</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q13</t>
         </is>
       </c>
       <c r="X60" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y60" s="6" t="inlineStr">
@@ -10195,7 +10197,7 @@
       </c>
       <c r="Z60" s="6" t="inlineStr">
         <is>
-          <t>Q11 | How likely are you to recommend the provider? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
+          <t>Q13 | Which improvement would have the greatest value? | single | Lower cost; Faster service; Clearer information; Better staff support; Improved digital experience | Randomize</t>
         </is>
       </c>
       <c r="AA60" s="6" t="inlineStr">
@@ -10215,7 +10217,7 @@
       </c>
       <c r="AD60" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE60" s="6" t="inlineStr">
@@ -10230,7 +10232,7 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>Q11</t>
+          <t>Q13</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
@@ -10245,12 +10247,12 @@
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>4. Randomization</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>8. Implementation Conformance</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
@@ -10260,17 +10262,17 @@
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>Q11 blocks a blank answer</t>
+          <t>Q13 shuffles without losing an option</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t>Prove Q11 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove Q13 still presents all 5 of its options when shuffled, with none dropped and none repeated.</t>
         </is>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Without a genuine shuffle the option order biases the answers, and without the recorded order the answers cannot be corrected later.</t>
         </is>
       </c>
       <c r="K61" s="6" t="inlineStr">
@@ -10280,7 +10282,7 @@
       </c>
       <c r="L61" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q11.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q13.</t>
         </is>
       </c>
       <c r="M61" s="6" t="inlineStr">
@@ -10290,33 +10292,33 @@
       </c>
       <c r="N61" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor
-then: At Q11, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not
+then: At Q13, choose “Lower cost”, then submit.</t>
         </is>
       </c>
       <c r="O61" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P61" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q11 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q11 is the one the claim turns on.</t>
+          <t>Every answer before Q13 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q13 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q61" s="6" t="inlineStr">
         <is>
-          <t>At Q11, select nothing at all, then submit.</t>
+          <t>At Q13, choose “Lower cost”, then submit.</t>
         </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11  (refused at Q11; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S61" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T61" s="6" t="inlineStr">
@@ -10326,23 +10328,23 @@
       </c>
       <c r="U61" s="6" t="inlineStr">
         <is>
-          <t>Q12, Q13, DT2, D1, D2, Q14</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V61" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W61" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q11</t>
+          <t>1. Q13 shows exactly 5 options, none missing or repeated
+2. the options shown at Q13 are exactly: Better staff support, Clearer information, Faster service, Improved digital experience, Lower cost</t>
         </is>
       </c>
       <c r="X61" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y61" s="6" t="inlineStr">
@@ -10352,7 +10354,7 @@
       </c>
       <c r="Z61" s="6" t="inlineStr">
         <is>
-          <t>Q11 | How likely are you to recommend the provider? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
+          <t>Q13 | Which improvement would have the greatest value? | single | Lower cost; Faster service; Clearer information; Better staff support; Improved digital experience | Randomize</t>
         </is>
       </c>
       <c r="AA61" s="6" t="inlineStr">
@@ -10372,7 +10374,7 @@
       </c>
       <c r="AD61" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove the order varies, only that nothing was lost or repeated. Order is a separate test needing several runs.</t>
         </is>
       </c>
       <c r="AE61" s="6" t="inlineStr">
@@ -10387,27 +10389,27 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>Q12</t>
+          <t>Q13</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>TC-FT54</t>
+          <t>TC-ST03</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>FOCUSED</t>
+          <t>STATEFUL</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>4. Randomization</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8. Implementation Conformance</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
@@ -10417,27 +10419,27 @@
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>Q12 accepts a normal answer and the survey moves on</t>
+          <t>Q13 genuinely varies its option order</t>
         </is>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q12 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q13 is genuinely shuffled: the option order must differ between respondents. If it never changes, shuffling was not switched on.</t>
         </is>
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>Without a genuine shuffle the option order biases the answers, and without the recorded order the answers cannot be corrected later.</t>
         </is>
       </c>
       <c r="K62" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L62" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q12.</t>
+          <t>Run this same path 5 times and compare the recorded option order between runs.</t>
         </is>
       </c>
       <c r="M62" s="6" t="inlineStr">
@@ -10447,8 +10449,8 @@
       </c>
       <c r="N62" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not
+then: At Q13, choose “Lower cost”, then submit.</t>
         </is>
       </c>
       <c r="O62" s="6" t="inlineStr">
@@ -10458,12 +10460,12 @@
       </c>
       <c r="P62" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q12 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q12 is the one the claim turns on.</t>
+          <t>Every answer before Q13 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q13 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q62" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q13, choose “Lower cost”, then submit.</t>
         </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
@@ -10493,8 +10495,7 @@
       </c>
       <c r="W62" s="6" t="inlineStr">
         <is>
-          <t>1. Q12 is on screen
-2. the next question shown is Q13</t>
+          <t>1. the option order at Q13 is NOT identical on every run</t>
         </is>
       </c>
       <c r="X62" s="6" t="inlineStr">
@@ -10509,7 +10510,7 @@
       </c>
       <c r="Z62" s="6" t="inlineStr">
         <is>
-          <t>Q12 | How likely are you to continue using the provider? | single | Definitely not; Probably not; Unsure; Probably; Definitely | Always show</t>
+          <t>Q13 | Which improvement would have the greatest value? | single | Lower cost; Faster service; Clearer information; Better staff support; Improved digital experience | Randomize</t>
         </is>
       </c>
       <c r="AA62" s="6" t="inlineStr">
@@ -10529,7 +10530,7 @@
       </c>
       <c r="AD62" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove any particular order is correct, only that the order is not fixed.</t>
         </is>
       </c>
       <c r="AE62" s="6" t="inlineStr">
@@ -10544,12 +10545,12 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>Q12</t>
+          <t>DT2</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>TC-FT55</t>
+          <t>TC-FT54</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -10559,12 +10560,12 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
@@ -10574,27 +10575,27 @@
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>Q12 blocks a blank answer</t>
+          <t>DT2 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
-          <t>Prove Q12 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove that answering DT2 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L63" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q12.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as DT2.</t>
         </is>
       </c>
       <c r="M63" s="6" t="inlineStr">
@@ -10604,33 +10605,33 @@
       </c>
       <c r="N63" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0
-then: At Q12, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O63" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P63" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q12 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q12 is the one the claim turns on.</t>
+          <t>Every answer before DT2 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at DT2 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q63" s="6" t="inlineStr">
         <is>
-          <t>At Q12, select nothing at all, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R63" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12  (refused at Q12; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S63" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T63" s="6" t="inlineStr">
@@ -10640,23 +10641,22 @@
       </c>
       <c r="U63" s="6" t="inlineStr">
         <is>
-          <t>Q13, DT2, D1, D2, Q14</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V63" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W63" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q12</t>
+          <t>1. the next question shown is D1</t>
         </is>
       </c>
       <c r="X63" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y63" s="6" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="Z63" s="6" t="inlineStr">
         <is>
-          <t>Q12 | How likely are you to continue using the provider? | single | Definitely not; Probably not; Unsure; Probably; Definitely | Always show</t>
+          <t>DT2 | You're almost done! Thank you for your answers. Just a few last questions about you to finish up. | text display | — | Always show</t>
         </is>
       </c>
       <c r="AA63" s="6" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="AD63" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE63" s="6" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>Q13</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>TC-FT56</t>
+          <t>TC-FT55</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>Q13 accepts a normal answer and the survey moves on</t>
+          <t>D1 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q13 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove that answering D1 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J64" s="6" t="inlineStr">
@@ -10751,7 +10751,7 @@
       </c>
       <c r="L64" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q13.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as D1.</t>
         </is>
       </c>
       <c r="M64" s="6" t="inlineStr">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="P64" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q13 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q13 is the one the claim turns on.</t>
+          <t>Every answer before D1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D1 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q64" s="6" t="inlineStr">
@@ -10807,8 +10807,8 @@
       </c>
       <c r="W64" s="6" t="inlineStr">
         <is>
-          <t>1. Q13 is on screen
-2. the next question shown is DT2</t>
+          <t>1. D1 is on screen
+2. the next question shown is D2</t>
         </is>
       </c>
       <c r="X64" s="6" t="inlineStr">
@@ -10823,7 +10823,7 @@
       </c>
       <c r="Z64" s="6" t="inlineStr">
         <is>
-          <t>Q13 | Which improvement would have the greatest value? | single | Lower cost; Faster service; Clearer information; Better staff support; Improved digital experience | Randomize</t>
+          <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
       <c r="AA64" s="6" t="inlineStr">
@@ -10858,12 +10858,12 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>Q13</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>TC-FT57</t>
+          <t>TC-FT56</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -10888,12 +10888,12 @@
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>Q13 blocks a blank answer</t>
+          <t>D1 blocks a blank answer</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>Prove Q13 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove D1 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J65" s="6" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="L65" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q13.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as D1.</t>
         </is>
       </c>
       <c r="M65" s="6" t="inlineStr">
@@ -10918,8 +10918,8 @@
       </c>
       <c r="N65" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not
-then: At Q13, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost
+then: At D1, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O65" s="6" t="inlineStr">
@@ -10929,22 +10929,22 @@
       </c>
       <c r="P65" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q13 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q13 is the one the claim turns on.</t>
+          <t>Every answer before D1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D1 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q65" s="6" t="inlineStr">
         <is>
-          <t>At Q13, select nothing at all, then submit.</t>
+          <t>At D1, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R65" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13  (refused at Q13; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1  (refused at D1; respondent stays put)</t>
         </is>
       </c>
       <c r="S65" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1</t>
         </is>
       </c>
       <c r="T65" s="6" t="inlineStr">
@@ -10954,7 +10954,7 @@
       </c>
       <c r="U65" s="6" t="inlineStr">
         <is>
-          <t>DT2, D1, D2, Q14</t>
+          <t>D2, Q14</t>
         </is>
       </c>
       <c r="V65" s="6" t="inlineStr">
@@ -10965,7 +10965,7 @@
       <c r="W65" s="6" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q13</t>
+2. an error message is shown against D1</t>
         </is>
       </c>
       <c r="X65" s="6" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="Z65" s="6" t="inlineStr">
         <is>
-          <t>Q13 | Which improvement would have the greatest value? | single | Lower cost; Faster service; Clearer information; Better staff support; Improved digital experience | Randomize</t>
+          <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
       <c r="AA65" s="6" t="inlineStr">
@@ -11015,12 +11015,12 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>Q13</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>TC-FT58</t>
+          <t>TC-FT57</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -11030,42 +11030,42 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>4. Randomization</t>
+          <t>5. Quota / Stateful</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>8. Implementation Conformance</t>
+          <t>6. Termination / Disposition</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>Q13 shuffles without losing an option</t>
+          <t>QUOTA_REGION admits a respondent while D1-O1 is open</t>
         </is>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>Prove Q13 still presents all 5 of its options when shuffled, with none dropped and none repeated.</t>
+          <t>Prove QUOTA_REGION lets a 'North' respondent through while that group is below its target.</t>
         </is>
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
-          <t>Without a genuine shuffle the option order biases the answers, and without the recorded order the answers cannot be corrected later.</t>
+          <t>Quotas decide who gets turned away. Getting this wrong unbalances the whole sample.</t>
         </is>
       </c>
       <c r="K66" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="L66" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q13.</t>
+          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as D1.</t>
         </is>
       </c>
       <c r="M66" s="6" t="inlineStr">
@@ -11075,8 +11075,8 @@
       </c>
       <c r="N66" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not
-then: At Q13, choose “Lower cost”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost
+then: At D1, choose “North”, then submit.</t>
         </is>
       </c>
       <c r="O66" s="6" t="inlineStr">
@@ -11086,12 +11086,12 @@
       </c>
       <c r="P66" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q13 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q13 is the one the claim turns on.</t>
+          <t>Every answer before D1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D1 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q66" s="6" t="inlineStr">
         <is>
-          <t>At Q13, choose “Lower cost”, then submit.</t>
+          <t>At D1, choose “North”, then submit.</t>
         </is>
       </c>
       <c r="R66" s="6" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="T66" s="6" t="inlineStr">
         <is>
-          <t>Q8, Q9, Q10</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U66" s="6" t="inlineStr">
@@ -11121,8 +11121,7 @@
       </c>
       <c r="W66" s="6" t="inlineStr">
         <is>
-          <t>1. Q13 shows exactly 5 options, none missing or repeated
-2. the options shown at Q13 are exactly: Better staff support, Clearer information, Faster service, Improved digital experience, Lower cost</t>
+          <t>1. the respondent is allowed to continue</t>
         </is>
       </c>
       <c r="X66" s="6" t="inlineStr">
@@ -11137,7 +11136,7 @@
       </c>
       <c r="Z66" s="6" t="inlineStr">
         <is>
-          <t>Q13 | Which improvement would have the greatest value? | single | Lower cost; Faster service; Clearer information; Better staff support; Improved digital experience | Randomize</t>
+          <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
       <c r="AA66" s="6" t="inlineStr">
@@ -11157,7 +11156,7 @@
       </c>
       <c r="AD66" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the order varies, only that nothing was lost or repeated. Order is a separate test needing several runs.</t>
+          <t>It does not prove the counting is accurate, only that the boundary behaves as stated at the moment tested.</t>
         </is>
       </c>
       <c r="AE66" s="6" t="inlineStr">
@@ -11172,57 +11171,57 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Q13</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>TC-ST03</t>
+          <t>TC-FT58</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>STATEFUL</t>
+          <t>FOCUSED</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>4. Randomization</t>
+          <t>5. Quota / Stateful</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>8. Implementation Conformance</t>
+          <t>6. Termination / Disposition</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>Q13 genuinely varies its option order</t>
+          <t>QUOTA_REGION admits a respondent while D1-O2 is open</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>Prove Q13 is genuinely shuffled: the option order must differ between respondents. If it never changes, shuffling was not switched on.</t>
+          <t>Prove QUOTA_REGION lets a 'South' respondent through while that group is below its target.</t>
         </is>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>Without a genuine shuffle the option order biases the answers, and without the recorded order the answers cannot be corrected later.</t>
+          <t>Quotas decide who gets turned away. Getting this wrong unbalances the whole sample.</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="L67" s="6" t="inlineStr">
         <is>
-          <t>Run this same path 5 times and compare the recorded option order between runs.</t>
+          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as D1.</t>
         </is>
       </c>
       <c r="M67" s="6" t="inlineStr">
@@ -11232,8 +11231,8 @@
       </c>
       <c r="N67" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not
-then: At Q13, choose “Lower cost”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost
+then: At D1, choose “South”, then submit.</t>
         </is>
       </c>
       <c r="O67" s="6" t="inlineStr">
@@ -11243,12 +11242,12 @@
       </c>
       <c r="P67" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q13 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q13 is the one the claim turns on.</t>
+          <t>Every answer before D1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D1 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q67" s="6" t="inlineStr">
         <is>
-          <t>At Q13, choose “Lower cost”, then submit.</t>
+          <t>At D1, choose “South”, then submit.</t>
         </is>
       </c>
       <c r="R67" s="6" t="inlineStr">
@@ -11263,7 +11262,7 @@
       </c>
       <c r="T67" s="6" t="inlineStr">
         <is>
-          <t>Q8, Q9, Q10</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U67" s="6" t="inlineStr">
@@ -11278,7 +11277,7 @@
       </c>
       <c r="W67" s="6" t="inlineStr">
         <is>
-          <t>1. the option order at Q13 is NOT identical on every run</t>
+          <t>1. the respondent is allowed to continue</t>
         </is>
       </c>
       <c r="X67" s="6" t="inlineStr">
@@ -11293,7 +11292,7 @@
       </c>
       <c r="Z67" s="6" t="inlineStr">
         <is>
-          <t>Q13 | Which improvement would have the greatest value? | single | Lower cost; Faster service; Clearer information; Better staff support; Improved digital experience | Randomize</t>
+          <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
       <c r="AA67" s="6" t="inlineStr">
@@ -11313,7 +11312,7 @@
       </c>
       <c r="AD67" s="6" t="inlineStr">
         <is>
-          <t>It does not prove any particular order is correct, only that the order is not fixed.</t>
+          <t>It does not prove the counting is accurate, only that the boundary behaves as stated at the moment tested.</t>
         </is>
       </c>
       <c r="AE67" s="6" t="inlineStr">
@@ -11328,7 +11327,7 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>DT2</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
@@ -11343,42 +11342,42 @@
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>5. Quota / Stateful</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6. Termination / Disposition</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>DT2 accepts a normal answer and the survey moves on</t>
+          <t>QUOTA_REGION admits a respondent while D1-O3 is open</t>
         </is>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering DT2 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove QUOTA_REGION lets a 'East' respondent through while that group is below its target.</t>
         </is>
       </c>
       <c r="J68" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>Quotas decide who gets turned away. Getting this wrong unbalances the whole sample.</t>
         </is>
       </c>
       <c r="K68" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="L68" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as DT2.</t>
+          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as D1.</t>
         </is>
       </c>
       <c r="M68" s="6" t="inlineStr">
@@ -11388,8 +11387,8 @@
       </c>
       <c r="N68" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost
+then: At D1, choose “East”, then submit.</t>
         </is>
       </c>
       <c r="O68" s="6" t="inlineStr">
@@ -11399,12 +11398,12 @@
       </c>
       <c r="P68" s="6" t="inlineStr">
         <is>
-          <t>Every answer before DT2 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at DT2 is the one the claim turns on.</t>
+          <t>Every answer before D1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D1 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q68" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At D1, choose “East”, then submit.</t>
         </is>
       </c>
       <c r="R68" s="6" t="inlineStr">
@@ -11419,7 +11418,7 @@
       </c>
       <c r="T68" s="6" t="inlineStr">
         <is>
-          <t>Q8, Q9, Q10</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U68" s="6" t="inlineStr">
@@ -11434,7 +11433,7 @@
       </c>
       <c r="W68" s="6" t="inlineStr">
         <is>
-          <t>1. the next question shown is D1</t>
+          <t>1. the respondent is allowed to continue</t>
         </is>
       </c>
       <c r="X68" s="6" t="inlineStr">
@@ -11449,7 +11448,7 @@
       </c>
       <c r="Z68" s="6" t="inlineStr">
         <is>
-          <t>DT2 | You're almost done! Thank you for your answers. Just a few last questions about you to finish up. | text display | — | Always show</t>
+          <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
       <c r="AA68" s="6" t="inlineStr">
@@ -11469,7 +11468,7 @@
       </c>
       <c r="AD68" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove the counting is accurate, only that the boundary behaves as stated at the moment tested.</t>
         </is>
       </c>
       <c r="AE68" s="6" t="inlineStr">
@@ -11499,42 +11498,42 @@
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>5. Quota / Stateful</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6. Termination / Disposition</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>D1 accepts a normal answer and the survey moves on</t>
+          <t>QUOTA_REGION admits a respondent while D1-O4 is open</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering D1 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove QUOTA_REGION lets a 'West' respondent through while that group is below its target.</t>
         </is>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>Quotas decide who gets turned away. Getting this wrong unbalances the whole sample.</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as D1.</t>
+          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as D1.</t>
         </is>
       </c>
       <c r="M69" s="6" t="inlineStr">
@@ -11544,8 +11543,8 @@
       </c>
       <c r="N69" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost
+then: At D1, choose “West”, then submit.</t>
         </is>
       </c>
       <c r="O69" s="6" t="inlineStr">
@@ -11560,7 +11559,7 @@
       </c>
       <c r="Q69" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At D1, choose “West”, then submit.</t>
         </is>
       </c>
       <c r="R69" s="6" t="inlineStr">
@@ -11575,7 +11574,7 @@
       </c>
       <c r="T69" s="6" t="inlineStr">
         <is>
-          <t>Q8, Q9, Q10</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U69" s="6" t="inlineStr">
@@ -11590,8 +11589,7 @@
       </c>
       <c r="W69" s="6" t="inlineStr">
         <is>
-          <t>1. D1 is on screen
-2. the next question shown is D2</t>
+          <t>1. the respondent is allowed to continue</t>
         </is>
       </c>
       <c r="X69" s="6" t="inlineStr">
@@ -11626,7 +11624,7 @@
       </c>
       <c r="AD69" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove the counting is accurate, only that the boundary behaves as stated at the moment tested.</t>
         </is>
       </c>
       <c r="AE69" s="6" t="inlineStr">
@@ -11656,42 +11654,42 @@
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>5. Quota / Stateful</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>6. Termination / Disposition</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>D1 blocks a blank answer</t>
+          <t>QUOTA_REGION admits a respondent while D1-O5 is open</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
-          <t>Prove D1 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove QUOTA_REGION lets a 'Central' respondent through while that group is below its target.</t>
         </is>
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Quotas decide who gets turned away. Getting this wrong unbalances the whole sample.</t>
         </is>
       </c>
       <c r="K70" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="L70" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as D1.</t>
+          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as D1.</t>
         </is>
       </c>
       <c r="M70" s="6" t="inlineStr">
@@ -11702,12 +11700,12 @@
       <c r="N70" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost
-then: At D1, select nothing at all, then submit.</t>
+then: At D1, choose “Central”, then submit.</t>
         </is>
       </c>
       <c r="O70" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P70" s="6" t="inlineStr">
@@ -11717,43 +11715,42 @@
       </c>
       <c r="Q70" s="6" t="inlineStr">
         <is>
-          <t>At D1, select nothing at all, then submit.</t>
+          <t>At D1, choose “Central”, then submit.</t>
         </is>
       </c>
       <c r="R70" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1  (refused at D1; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S70" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T70" s="6" t="inlineStr">
         <is>
-          <t>Q8, Q9, Q10</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U70" s="6" t="inlineStr">
         <is>
-          <t>D2, Q14</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V70" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W70" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against D1</t>
+          <t>1. the respondent is allowed to continue</t>
         </is>
       </c>
       <c r="X70" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y70" s="6" t="inlineStr">
@@ -11783,7 +11780,7 @@
       </c>
       <c r="AD70" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove the counting is accurate, only that the boundary behaves as stated at the moment tested.</t>
         </is>
       </c>
       <c r="AE70" s="6" t="inlineStr">
@@ -11798,7 +11795,7 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
@@ -11813,42 +11810,42 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>5. Quota / Stateful</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>6. Termination / Disposition</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>QUOTA_REGION admits a respondent while D1-O1 is open</t>
+          <t>D2 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>Prove QUOTA_REGION lets a 'North' respondent through while that group is below its target.</t>
+          <t>Prove that answering D2 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>Quotas decide who gets turned away. Getting this wrong unbalances the whole sample.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L71" s="6" t="inlineStr">
         <is>
-          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as D1.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as D2.</t>
         </is>
       </c>
       <c r="M71" s="6" t="inlineStr">
@@ -11858,8 +11855,8 @@
       </c>
       <c r="N71" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost
-then: At D1, choose “North”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O71" s="6" t="inlineStr">
@@ -11869,12 +11866,12 @@
       </c>
       <c r="P71" s="6" t="inlineStr">
         <is>
-          <t>Every answer before D1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D1 is the one the claim turns on.</t>
+          <t>Every answer before D2 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D2 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q71" s="6" t="inlineStr">
         <is>
-          <t>At D1, choose “North”, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R71" s="6" t="inlineStr">
@@ -11889,14 +11886,14 @@
       </c>
       <c r="T71" s="6" t="inlineStr">
         <is>
+          <t>Q8, Q9, Q10</t>
+        </is>
+      </c>
+      <c r="U71" s="6" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="U71" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
       <c r="V71" s="6" t="inlineStr">
         <is>
           <t>Each listed question is followed immediately by the next in the sequence.</t>
@@ -11904,7 +11901,8 @@
       </c>
       <c r="W71" s="6" t="inlineStr">
         <is>
-          <t>1. the respondent is allowed to continue</t>
+          <t>1. D2 is on screen
+2. the next question shown is Q14</t>
         </is>
       </c>
       <c r="X71" s="6" t="inlineStr">
@@ -11919,7 +11917,7 @@
       </c>
       <c r="Z71" s="6" t="inlineStr">
         <is>
-          <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
+          <t>D2 | Which age group describes you? | single | 18-24; 25-34; 35-44; 45-54; 55+ | Always show</t>
         </is>
       </c>
       <c r="AA71" s="6" t="inlineStr">
@@ -11939,7 +11937,7 @@
       </c>
       <c r="AD71" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the counting is accurate, only that the boundary behaves as stated at the moment tested.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE71" s="6" t="inlineStr">
@@ -11954,7 +11952,7 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
@@ -11969,42 +11967,42 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>5. Quota / Stateful</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>6. Termination / Disposition</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>QUOTA_REGION admits a respondent while D1-O2 is open</t>
+          <t>D2 blocks a blank answer</t>
         </is>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
-          <t>Prove QUOTA_REGION lets a 'South' respondent through while that group is below its target.</t>
+          <t>Prove D2 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
-          <t>Quotas decide who gets turned away. Getting this wrong unbalances the whole sample.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K72" s="6" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L72" s="6" t="inlineStr">
         <is>
-          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as D1.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as D2.</t>
         </is>
       </c>
       <c r="M72" s="6" t="inlineStr">
@@ -12014,58 +12012,59 @@
       </c>
       <c r="N72" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost
-then: At D1, choose “South”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North
+then: At D2, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O72" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P72" s="6" t="inlineStr">
         <is>
-          <t>Every answer before D1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D1 is the one the claim turns on.</t>
+          <t>Every answer before D2 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D2 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q72" s="6" t="inlineStr">
         <is>
-          <t>At D1, choose “South”, then submit.</t>
+          <t>At D2, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R72" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2  (refused at D2; respondent stays put)</t>
         </is>
       </c>
       <c r="S72" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2</t>
         </is>
       </c>
       <c r="T72" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q8, Q9, Q10</t>
         </is>
       </c>
       <c r="U72" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q14</t>
         </is>
       </c>
       <c r="V72" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W72" s="6" t="inlineStr">
         <is>
-          <t>1. the respondent is allowed to continue</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against D2</t>
         </is>
       </c>
       <c r="X72" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y72" s="6" t="inlineStr">
@@ -12075,7 +12074,7 @@
       </c>
       <c r="Z72" s="6" t="inlineStr">
         <is>
-          <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
+          <t>D2 | Which age group describes you? | single | 18-24; 25-34; 35-44; 45-54; 55+ | Always show</t>
         </is>
       </c>
       <c r="AA72" s="6" t="inlineStr">
@@ -12095,7 +12094,7 @@
       </c>
       <c r="AD72" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the counting is accurate, only that the boundary behaves as stated at the moment tested.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE72" s="6" t="inlineStr">
@@ -12110,7 +12109,7 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>Q14</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
@@ -12125,42 +12124,42 @@
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>5. Quota / Stateful</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>6. Termination / Disposition</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>QUOTA_REGION admits a respondent while D1-O3 is open</t>
+          <t>Q14 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
-          <t>Prove QUOTA_REGION lets a 'East' respondent through while that group is below its target.</t>
+          <t>Prove that answering Q14 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>Quotas decide who gets turned away. Getting this wrong unbalances the whole sample.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr">
         <is>
-          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as D1.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q14.</t>
         </is>
       </c>
       <c r="M73" s="6" t="inlineStr">
@@ -12170,8 +12169,8 @@
       </c>
       <c r="N73" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost
-then: At D1, choose “East”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O73" s="6" t="inlineStr">
@@ -12181,12 +12180,12 @@
       </c>
       <c r="P73" s="6" t="inlineStr">
         <is>
-          <t>Every answer before D1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D1 is the one the claim turns on.</t>
+          <t>Every answer before Q14 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q14 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q73" s="6" t="inlineStr">
         <is>
-          <t>At D1, choose “East”, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R73" s="6" t="inlineStr">
@@ -12201,14 +12200,14 @@
       </c>
       <c r="T73" s="6" t="inlineStr">
         <is>
+          <t>Q8, Q9, Q10</t>
+        </is>
+      </c>
+      <c r="U73" s="6" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="U73" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
       <c r="V73" s="6" t="inlineStr">
         <is>
           <t>Each listed question is followed immediately by the next in the sequence.</t>
@@ -12216,7 +12215,8 @@
       </c>
       <c r="W73" s="6" t="inlineStr">
         <is>
-          <t>1. the respondent is allowed to continue</t>
+          <t>1. Q14 is on screen
+2. the respondent reaches the normal thank-you page</t>
         </is>
       </c>
       <c r="X73" s="6" t="inlineStr">
@@ -12231,7 +12231,8 @@
       </c>
       <c r="Z73" s="6" t="inlineStr">
         <is>
-          <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
+          <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
+Optional</t>
         </is>
       </c>
       <c r="AA73" s="6" t="inlineStr">
@@ -12251,7 +12252,7 @@
       </c>
       <c r="AD73" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the counting is accurate, only that the boundary behaves as stated at the moment tested.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE73" s="6" t="inlineStr">
@@ -12266,7 +12267,7 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>Q14</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
@@ -12281,42 +12282,42 @@
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>5. Quota / Stateful</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>6. Termination / Disposition</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>QUOTA_REGION admits a respondent while D1-O4 is open</t>
+          <t>Q14 accepts a valid answer</t>
         </is>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
-          <t>Prove QUOTA_REGION lets a 'West' respondent through while that group is below its target.</t>
+          <t>Prove Q14 accepts an answer that obeys its stated rule. The rule is: at most 750 characters</t>
         </is>
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
-          <t>Quotas decide who gets turned away. Getting this wrong unbalances the whole sample.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K74" s="6" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L74" s="6" t="inlineStr">
         <is>
-          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as D1.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q14.</t>
         </is>
       </c>
       <c r="M74" s="6" t="inlineStr">
@@ -12326,23 +12327,23 @@
       </c>
       <c r="N74" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost
-then: At D1, choose “West”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: At Q14, type “x”, then submit.</t>
         </is>
       </c>
       <c r="O74" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>VALID_BOUNDARY</t>
         </is>
       </c>
       <c r="P74" s="6" t="inlineStr">
         <is>
-          <t>Every answer before D1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D1 is the one the claim turns on.</t>
+          <t>Every answer before Q14 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q14 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q74" s="6" t="inlineStr">
         <is>
-          <t>At D1, choose “West”, then submit.</t>
+          <t>At Q14, type “x”, then submit.</t>
         </is>
       </c>
       <c r="R74" s="6" t="inlineStr">
@@ -12357,14 +12358,14 @@
       </c>
       <c r="T74" s="6" t="inlineStr">
         <is>
+          <t>Q8, Q9, Q10</t>
+        </is>
+      </c>
+      <c r="U74" s="6" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="U74" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
       <c r="V74" s="6" t="inlineStr">
         <is>
           <t>Each listed question is followed immediately by the next in the sequence.</t>
@@ -12372,7 +12373,7 @@
       </c>
       <c r="W74" s="6" t="inlineStr">
         <is>
-          <t>1. the respondent is allowed to continue</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X74" s="6" t="inlineStr">
@@ -12387,7 +12388,8 @@
       </c>
       <c r="Z74" s="6" t="inlineStr">
         <is>
-          <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
+          <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
+Optional</t>
         </is>
       </c>
       <c r="AA74" s="6" t="inlineStr">
@@ -12407,7 +12409,7 @@
       </c>
       <c r="AD74" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the counting is accurate, only that the boundary behaves as stated at the moment tested.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE74" s="6" t="inlineStr">
@@ -12422,7 +12424,7 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>Q14</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
@@ -12437,42 +12439,42 @@
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>5. Quota / Stateful</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>6. Termination / Disposition</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>QUOTA_REGION admits a respondent while D1-O5 is open</t>
+          <t>Q14 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
-          <t>Prove QUOTA_REGION lets a 'Central' respondent through while that group is below its target.</t>
+          <t>Prove Q14 refuses an answer that breaks its stated rule. The rule is: at most 750 characters</t>
         </is>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>Quotas decide who gets turned away. Getting this wrong unbalances the whole sample.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr">
         <is>
-          <t>Travel path P03 (QUOTA_REGION cell already full (North) — measured on D1) as far as D1.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q14.</t>
         </is>
       </c>
       <c r="M75" s="6" t="inlineStr">
@@ -12482,28 +12484,28 @@
       </c>
       <c r="N75" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost
-then: At D1, choose “Central”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: At Q14, type a 751-character answer, then submit.</t>
         </is>
       </c>
       <c r="O75" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>INVALID_BOUNDARY</t>
         </is>
       </c>
       <c r="P75" s="6" t="inlineStr">
         <is>
-          <t>Every answer before D1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D1 is the one the claim turns on.</t>
+          <t>Every answer before Q14 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q14 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q75" s="6" t="inlineStr">
         <is>
-          <t>At D1, choose “Central”, then submit.</t>
+          <t>At Q14, type a 751-character answer, then submit.</t>
         </is>
       </c>
       <c r="R75" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14  (refused at Q14; respondent stays put)</t>
         </is>
       </c>
       <c r="S75" s="6" t="inlineStr">
@@ -12513,27 +12515,28 @@
       </c>
       <c r="T75" s="6" t="inlineStr">
         <is>
+          <t>Q8, Q9, Q10</t>
+        </is>
+      </c>
+      <c r="U75" s="6" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="U75" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
       <c r="V75" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W75" s="6" t="inlineStr">
         <is>
-          <t>1. the respondent is allowed to continue</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q14</t>
         </is>
       </c>
       <c r="X75" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y75" s="6" t="inlineStr">
@@ -12543,7 +12546,8 @@
       </c>
       <c r="Z75" s="6" t="inlineStr">
         <is>
-          <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
+          <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
+Optional</t>
         </is>
       </c>
       <c r="AA75" s="6" t="inlineStr">
@@ -12563,7 +12567,7 @@
       </c>
       <c r="AD75" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the counting is accurate, only that the boundary behaves as stated at the moment tested.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE75" s="6" t="inlineStr">
@@ -12578,7 +12582,7 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>Q14</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
@@ -12593,7 +12597,7 @@
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
@@ -12608,27 +12612,27 @@
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>D2 accepts a normal answer and the survey moves on</t>
+          <t>Q14 allows a blank answer, being optional</t>
         </is>
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering D2 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q14 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
         </is>
       </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K76" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L76" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as D2.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q14.</t>
         </is>
       </c>
       <c r="M76" s="6" t="inlineStr">
@@ -12639,22 +12643,22 @@
       <c r="N76" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+then: At Q14, type nothing, then submit.</t>
         </is>
       </c>
       <c r="O76" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P76" s="6" t="inlineStr">
         <is>
-          <t>Every answer before D2 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D2 is the one the claim turns on.</t>
+          <t>Every answer before Q14 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q14 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q76" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q14, type nothing, then submit.</t>
         </is>
       </c>
       <c r="R76" s="6" t="inlineStr">
@@ -12684,8 +12688,7 @@
       </c>
       <c r="W76" s="6" t="inlineStr">
         <is>
-          <t>1. D2 is on screen
-2. the next question shown is Q14</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X76" s="6" t="inlineStr">
@@ -12700,7 +12703,8 @@
       </c>
       <c r="Z76" s="6" t="inlineStr">
         <is>
-          <t>D2 | Which age group describes you? | single | 18-24; 25-34; 35-44; 45-54; 55+ | Always show</t>
+          <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
+Optional</t>
         </is>
       </c>
       <c r="AA76" s="6" t="inlineStr">
@@ -12720,7 +12724,7 @@
       </c>
       <c r="AD76" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE76" s="6" t="inlineStr">
@@ -12735,7 +12739,7 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>Q14</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
@@ -12755,7 +12759,7 @@
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
@@ -12765,27 +12769,27 @@
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>D2 blocks a blank answer</t>
+          <t>Q14 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
-          <t>Prove D2 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove Q14 refuses an answer that breaks its stated rule. The rule is: at most 750 characters</t>
         </is>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as D2.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q14.</t>
         </is>
       </c>
       <c r="M77" s="6" t="inlineStr">
@@ -12795,33 +12799,33 @@
       </c>
       <c r="N77" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North
-then: At D2, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
+then: At Q14, type a 750-character answer, then submit.</t>
         </is>
       </c>
       <c r="O77" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P77" s="6" t="inlineStr">
         <is>
-          <t>Every answer before D2 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D2 is the one the claim turns on.</t>
+          <t>Every answer before Q14 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q14 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q77" s="6" t="inlineStr">
         <is>
-          <t>At D2, select nothing at all, then submit.</t>
+          <t>At Q14, type a 750-character answer, then submit.</t>
         </is>
       </c>
       <c r="R77" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2  (refused at D2; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
       <c r="S77" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2</t>
+          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
       <c r="T77" s="6" t="inlineStr">
@@ -12831,23 +12835,22 @@
       </c>
       <c r="U77" s="6" t="inlineStr">
         <is>
-          <t>Q14</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V77" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W77" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against D2</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X77" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y77" s="6" t="inlineStr">
@@ -12857,7 +12860,8 @@
       </c>
       <c r="Z77" s="6" t="inlineStr">
         <is>
-          <t>D2 | Which age group describes you? | single | 18-24; 25-34; 35-44; 45-54; 55+ | Always show</t>
+          <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
+Optional</t>
         </is>
       </c>
       <c r="AA77" s="6" t="inlineStr">
@@ -12877,7 +12881,7 @@
       </c>
       <c r="AD77" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE77" s="6" t="inlineStr">
@@ -12907,7 +12911,7 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
@@ -12922,17 +12926,17 @@
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>Q14 accepts a normal answer and the survey moves on</t>
+          <t>Q14 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q14 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q14 refuses an answer that breaks its stated rule. The rule is: at most 750 characters</t>
         </is>
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K78" s="6" t="inlineStr">
@@ -12953,7 +12957,7 @@
       <c r="N78" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+then: At Q14, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="O78" s="6" t="inlineStr">
@@ -12968,7 +12972,7 @@
       </c>
       <c r="Q78" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q14, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="R78" s="6" t="inlineStr">
@@ -12998,8 +13002,7 @@
       </c>
       <c r="W78" s="6" t="inlineStr">
         <is>
-          <t>1. Q14 is on screen
-2. the respondent reaches the normal thank-you page</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X78" s="6" t="inlineStr">
@@ -13035,7 +13038,7 @@
       </c>
       <c r="AD78" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE78" s="6" t="inlineStr">
@@ -13080,22 +13083,22 @@
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>Q14 accepts a valid answer</t>
+          <t>Q14 allows a blank answer, being optional</t>
         </is>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
-          <t>Prove Q14 accepts an answer that obeys its stated rule. The rule is: at most 750 characters</t>
+          <t>Prove Q14 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
         </is>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr">
@@ -13111,12 +13114,12 @@
       <c r="N79" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: At Q14, type “x”, then submit.</t>
+then: At Q14, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="O79" s="6" t="inlineStr">
         <is>
-          <t>VALID_BOUNDARY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P79" s="6" t="inlineStr">
@@ -13126,7 +13129,7 @@
       </c>
       <c r="Q79" s="6" t="inlineStr">
         <is>
-          <t>At Q14, type “x”, then submit.</t>
+          <t>At Q14, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="R79" s="6" t="inlineStr">
@@ -13192,12 +13195,12 @@
       </c>
       <c r="AD79" s="6" t="inlineStr">
         <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE79" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: multi_equality</t>
+          <t>Leans on an unconfirmed reading: multi_equality, whitespace_is_an_answer</t>
         </is>
       </c>
     </row>
@@ -13207,27 +13210,27 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Q14</t>
+          <t>whole survey</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>TC-FT71</t>
+          <t>TC-RT03</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>FOCUSED</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>6. Termination / Disposition</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
@@ -13237,27 +13240,27 @@
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>Q14 rejects an invalid answer</t>
+          <t>End-to-end journey: COMPLETE by way of routing</t>
         </is>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
-          <t>Prove Q14 refuses an answer that breaks its stated rule. The rule is: at most 750 characters</t>
+          <t>Prove that a respondent answering as listed is shown exactly this sequence of questions, in this order, and ends at COMPLETE by way of the routing, checked at ?. Condition: . They should then see: “Thank you. Your response has been recorded.”</t>
         </is>
       </c>
       <c r="J80" s="6" t="inlineStr">
         <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+          <t>Screening someone out incorrectly loses a valid respondent and the money spent recruiting them. Failing to screen someone out puts the wrong person in the sample.</t>
         </is>
       </c>
       <c r="K80" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="L80" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q14.</t>
+          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as the end.</t>
         </is>
       </c>
       <c r="M80" s="6" t="inlineStr">
@@ -13266,878 +13269,92 @@
         </is>
       </c>
       <c r="N80" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: At Q14, type a 751-character answer, then submit.</t>
-        </is>
-      </c>
-      <c r="O80" s="6" t="inlineStr">
-        <is>
-          <t>INVALID_BOUNDARY</t>
-        </is>
-      </c>
-      <c r="P80" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q14 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q14 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q80" s="6" t="inlineStr">
-        <is>
-          <t>At Q14, type a 751-character answer, then submit.</t>
-        </is>
-      </c>
-      <c r="R80" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14  (refused at Q14; respondent stays put)</t>
-        </is>
-      </c>
-      <c r="S80" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
-        </is>
-      </c>
-      <c r="T80" s="6" t="inlineStr">
-        <is>
-          <t>Q8, Q9, Q10</t>
-        </is>
-      </c>
-      <c r="U80" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="V80" s="6" t="inlineStr">
-        <is>
-          <t>No forward navigation - the same question must reappear.</t>
-        </is>
-      </c>
-      <c r="W80" s="6" t="inlineStr">
-        <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q14</t>
-        </is>
-      </c>
-      <c r="X80" s="6" t="inlineStr">
-        <is>
-          <t>Not reached - the respondent cannot progress</t>
-        </is>
-      </c>
-      <c r="Y80" s="6" t="inlineStr">
-        <is>
-          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
-        </is>
-      </c>
-      <c r="Z80" s="6" t="inlineStr">
-        <is>
-          <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
-Optional</t>
-        </is>
-      </c>
-      <c r="AA80" s="6" t="inlineStr">
-        <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB80" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="AC80" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AD80" s="6" t="inlineStr">
-        <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
-        </is>
-      </c>
-      <c r="AE80" s="6" t="inlineStr">
-        <is>
-          <t>Leans on an unconfirmed reading: multi_equality</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="4" t="n">
-        <v>77</v>
-      </c>
-      <c r="B81" s="9" t="inlineStr">
-        <is>
-          <t>Q14</t>
-        </is>
-      </c>
-      <c r="C81" s="7" t="inlineStr">
-        <is>
-          <t>TC-FT72</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>FOCUSED</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>2. Input Validation</t>
-        </is>
-      </c>
-      <c r="F81" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G81" s="7" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="H81" s="6" t="inlineStr">
-        <is>
-          <t>Q14 allows a blank answer, being optional</t>
-        </is>
-      </c>
-      <c r="I81" s="6" t="inlineStr">
-        <is>
-          <t>Prove Q14 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
-        </is>
-      </c>
-      <c r="J81" s="6" t="inlineStr">
-        <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
-        </is>
-      </c>
-      <c r="K81" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L81" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q14.</t>
-        </is>
-      </c>
-      <c r="M81" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N81" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: At Q14, type nothing, then submit.</t>
-        </is>
-      </c>
-      <c r="O81" s="6" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="P81" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q14 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q14 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q81" s="6" t="inlineStr">
-        <is>
-          <t>At Q14, type nothing, then submit.</t>
-        </is>
-      </c>
-      <c r="R81" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
-        </is>
-      </c>
-      <c r="S81" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
-        </is>
-      </c>
-      <c r="T81" s="6" t="inlineStr">
-        <is>
-          <t>Q8, Q9, Q10</t>
-        </is>
-      </c>
-      <c r="U81" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="V81" s="6" t="inlineStr">
-        <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
-        </is>
-      </c>
-      <c r="W81" s="6" t="inlineStr">
-        <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
-        </is>
-      </c>
-      <c r="X81" s="6" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="Y81" s="6" t="inlineStr">
-        <is>
-          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
-        </is>
-      </c>
-      <c r="Z81" s="6" t="inlineStr">
-        <is>
-          <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
-Optional</t>
-        </is>
-      </c>
-      <c r="AA81" s="6" t="inlineStr">
-        <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB81" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="AC81" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AD81" s="6" t="inlineStr">
-        <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
-        </is>
-      </c>
-      <c r="AE81" s="6" t="inlineStr">
-        <is>
-          <t>Leans on an unconfirmed reading: multi_equality</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="4" t="n">
-        <v>78</v>
-      </c>
-      <c r="B82" s="9" t="inlineStr">
-        <is>
-          <t>Q14</t>
-        </is>
-      </c>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>TC-FT73</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>FOCUSED</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>2. Input Validation</t>
-        </is>
-      </c>
-      <c r="F82" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G82" s="7" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="H82" s="6" t="inlineStr">
-        <is>
-          <t>Q14 rejects an invalid answer</t>
-        </is>
-      </c>
-      <c r="I82" s="6" t="inlineStr">
-        <is>
-          <t>Prove Q14 refuses an answer that breaks its stated rule. The rule is: at most 750 characters</t>
-        </is>
-      </c>
-      <c r="J82" s="6" t="inlineStr">
-        <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
-        </is>
-      </c>
-      <c r="K82" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L82" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q14.</t>
-        </is>
-      </c>
-      <c r="M82" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N82" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: At Q14, type a 750-character answer, then submit.</t>
-        </is>
-      </c>
-      <c r="O82" s="6" t="inlineStr">
-        <is>
-          <t>VALID_TYPICAL for every answer</t>
-        </is>
-      </c>
-      <c r="P82" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q14 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q14 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q82" s="6" t="inlineStr">
-        <is>
-          <t>At Q14, type a 750-character answer, then submit.</t>
-        </is>
-      </c>
-      <c r="R82" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
-        </is>
-      </c>
-      <c r="S82" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
-        </is>
-      </c>
-      <c r="T82" s="6" t="inlineStr">
-        <is>
-          <t>Q8, Q9, Q10</t>
-        </is>
-      </c>
-      <c r="U82" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="V82" s="6" t="inlineStr">
-        <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
-        </is>
-      </c>
-      <c r="W82" s="6" t="inlineStr">
-        <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
-        </is>
-      </c>
-      <c r="X82" s="6" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="Y82" s="6" t="inlineStr">
-        <is>
-          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
-        </is>
-      </c>
-      <c r="Z82" s="6" t="inlineStr">
-        <is>
-          <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
-Optional</t>
-        </is>
-      </c>
-      <c r="AA82" s="6" t="inlineStr">
-        <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB82" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="AC82" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AD82" s="6" t="inlineStr">
-        <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
-        </is>
-      </c>
-      <c r="AE82" s="6" t="inlineStr">
-        <is>
-          <t>Leans on an unconfirmed reading: multi_equality</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="4" t="n">
-        <v>79</v>
-      </c>
-      <c r="B83" s="9" t="inlineStr">
-        <is>
-          <t>Q14</t>
-        </is>
-      </c>
-      <c r="C83" s="7" t="inlineStr">
-        <is>
-          <t>TC-FT74</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>FOCUSED</t>
-        </is>
-      </c>
-      <c r="E83" s="6" t="inlineStr">
-        <is>
-          <t>2. Input Validation</t>
-        </is>
-      </c>
-      <c r="F83" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G83" s="7" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="H83" s="6" t="inlineStr">
-        <is>
-          <t>Q14 rejects an invalid answer</t>
-        </is>
-      </c>
-      <c r="I83" s="6" t="inlineStr">
-        <is>
-          <t>Prove Q14 refuses an answer that breaks its stated rule. The rule is: at most 750 characters</t>
-        </is>
-      </c>
-      <c r="J83" s="6" t="inlineStr">
-        <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
-        </is>
-      </c>
-      <c r="K83" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L83" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q14.</t>
-        </is>
-      </c>
-      <c r="M83" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N83" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: At Q14, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
-        </is>
-      </c>
-      <c r="O83" s="6" t="inlineStr">
-        <is>
-          <t>VALID_TYPICAL for every answer</t>
-        </is>
-      </c>
-      <c r="P83" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q14 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q14 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q83" s="6" t="inlineStr">
-        <is>
-          <t>At Q14, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
-        </is>
-      </c>
-      <c r="R83" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
-        </is>
-      </c>
-      <c r="S83" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
-        </is>
-      </c>
-      <c r="T83" s="6" t="inlineStr">
-        <is>
-          <t>Q8, Q9, Q10</t>
-        </is>
-      </c>
-      <c r="U83" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="V83" s="6" t="inlineStr">
-        <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
-        </is>
-      </c>
-      <c r="W83" s="6" t="inlineStr">
-        <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
-        </is>
-      </c>
-      <c r="X83" s="6" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="Y83" s="6" t="inlineStr">
-        <is>
-          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
-        </is>
-      </c>
-      <c r="Z83" s="6" t="inlineStr">
-        <is>
-          <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
-Optional</t>
-        </is>
-      </c>
-      <c r="AA83" s="6" t="inlineStr">
-        <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB83" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="AC83" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AD83" s="6" t="inlineStr">
-        <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
-        </is>
-      </c>
-      <c r="AE83" s="6" t="inlineStr">
-        <is>
-          <t>Leans on an unconfirmed reading: multi_equality</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t>Q14</t>
-        </is>
-      </c>
-      <c r="C84" s="7" t="inlineStr">
-        <is>
-          <t>TC-FT75</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>FOCUSED</t>
-        </is>
-      </c>
-      <c r="E84" s="6" t="inlineStr">
-        <is>
-          <t>2. Input Validation</t>
-        </is>
-      </c>
-      <c r="F84" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G84" s="7" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="H84" s="6" t="inlineStr">
-        <is>
-          <t>Q14 allows a blank answer, being optional</t>
-        </is>
-      </c>
-      <c r="I84" s="6" t="inlineStr">
-        <is>
-          <t>Prove Q14 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
-        </is>
-      </c>
-      <c r="J84" s="6" t="inlineStr">
-        <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
-        </is>
-      </c>
-      <c r="K84" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L84" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as Q14.</t>
-        </is>
-      </c>
-      <c r="M84" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N84" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
-then: At Q14, type 3 spaces and nothing else, then submit.</t>
-        </is>
-      </c>
-      <c r="O84" s="6" t="inlineStr">
-        <is>
-          <t>VALID_TYPICAL for every answer</t>
-        </is>
-      </c>
-      <c r="P84" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q14 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q14 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q84" s="6" t="inlineStr">
-        <is>
-          <t>At Q14, type 3 spaces and nothing else, then submit.</t>
-        </is>
-      </c>
-      <c r="R84" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
-        </is>
-      </c>
-      <c r="S84" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
-        </is>
-      </c>
-      <c r="T84" s="6" t="inlineStr">
-        <is>
-          <t>Q8, Q9, Q10</t>
-        </is>
-      </c>
-      <c r="U84" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="V84" s="6" t="inlineStr">
-        <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
-        </is>
-      </c>
-      <c r="W84" s="6" t="inlineStr">
-        <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
-        </is>
-      </c>
-      <c r="X84" s="6" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="Y84" s="6" t="inlineStr">
-        <is>
-          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
-        </is>
-      </c>
-      <c r="Z84" s="6" t="inlineStr">
-        <is>
-          <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
-Optional</t>
-        </is>
-      </c>
-      <c r="AA84" s="6" t="inlineStr">
-        <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB84" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="AC84" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AD84" s="6" t="inlineStr">
-        <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
-        </is>
-      </c>
-      <c r="AE84" s="6" t="inlineStr">
-        <is>
-          <t>Leans on an unconfirmed reading: multi_equality, whitespace_is_an_answer</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="4" t="n">
-        <v>81</v>
-      </c>
-      <c r="B85" s="9" t="inlineStr">
-        <is>
-          <t>whole survey</t>
-        </is>
-      </c>
-      <c r="C85" s="7" t="inlineStr">
-        <is>
-          <t>TC-RT03</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>ROUTE</t>
-        </is>
-      </c>
-      <c r="E85" s="6" t="inlineStr">
-        <is>
-          <t>6. Termination / Disposition</t>
-        </is>
-      </c>
-      <c r="F85" s="6" t="inlineStr">
-        <is>
-          <t>1. Flow / Routing</t>
-        </is>
-      </c>
-      <c r="G85" s="7" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="H85" s="6" t="inlineStr">
-        <is>
-          <t>End-to-end journey: COMPLETE by way of routing</t>
-        </is>
-      </c>
-      <c r="I85" s="6" t="inlineStr">
-        <is>
-          <t>Prove that a respondent answering as listed is shown exactly this sequence of questions, in this order, and ends at COMPLETE by way of the routing, checked at ?. Condition: . They should then see: “Thank you. Your response has been recorded.”</t>
-        </is>
-      </c>
-      <c r="J85" s="6" t="inlineStr">
-        <is>
-          <t>Screening someone out incorrectly loses a valid respondent and the money spent recruiting them. Failing to screen someone out puts the wrong person in the sample.</t>
-        </is>
-      </c>
-      <c r="K85" s="6" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="L85" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P04 (Completing respondent — Q7=None of these) as far as the end.</t>
-        </is>
-      </c>
-      <c r="M85" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N85" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; S3 = 18; Q1 = Hotel A; Q2 = Within 7 days; Q3 = Business trip; Q4 = Very poor; Q5 = Very poor; Q6 = Very poor; Q7 = Room cleanliness; Q8 = Room cleanliness; Q9 = Yes, fully; Q10 = Very poor; Q11 = 0; Q12 = Definitely not; Q13 = Lower cost; D1 = North; D2 = 18-24
 then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="O85" s="6" t="inlineStr">
+      <c r="O80" s="6" t="inlineStr">
         <is>
           <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
-      <c r="P85" s="6" t="inlineStr">
+      <c r="P80" s="6" t="inlineStr">
         <is>
           <t>Chosen to walk the whole survey without triggering a screen-out.</t>
         </is>
       </c>
-      <c r="Q85" s="6" t="inlineStr">
+      <c r="Q80" s="6" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="R85" s="6" t="inlineStr">
+      <c r="R80" s="6" t="inlineStr">
         <is>
           <t>S1 -&gt; S2 -&gt; S3 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; DT2 -&gt; D1 -&gt; D2 -&gt; Q14</t>
         </is>
       </c>
-      <c r="S85" s="6" t="inlineStr">
+      <c r="S80" s="6" t="inlineStr">
         <is>
           <t>S1, S2, S3, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, DT2, D1, D2, Q14</t>
         </is>
       </c>
-      <c r="T85" s="6" t="inlineStr">
+      <c r="T80" s="6" t="inlineStr">
         <is>
           <t>Q8, Q9, Q10</t>
         </is>
       </c>
-      <c r="U85" s="6" t="inlineStr">
+      <c r="U80" s="6" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="V85" s="6" t="inlineStr">
+      <c r="V80" s="6" t="inlineStr">
         <is>
           <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
-      <c r="W85" s="6" t="inlineStr">
+      <c r="W80" s="6" t="inlineStr">
         <is>
           <t>1. the respondent reaches the normal thank-you page</t>
         </is>
       </c>
-      <c r="X85" s="6" t="inlineStr">
+      <c r="X80" s="6" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
       </c>
-      <c r="Y85" s="6" t="inlineStr">
+      <c r="Y80" s="6" t="inlineStr">
         <is>
           <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
         </is>
       </c>
-      <c r="Z85" s="6" t="inlineStr">
+      <c r="Z80" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AA85" s="6" t="inlineStr">
+      <c r="AA80" s="6" t="inlineStr">
         <is>
           <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
-      <c r="AB85" s="10" t="inlineStr">
+      <c r="AB80" s="10" t="inlineStr">
         <is>
           <t>PROVISIONAL</t>
         </is>
       </c>
-      <c r="AC85" s="8" t="inlineStr">
+      <c r="AC80" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AD85" s="6" t="inlineStr">
+      <c r="AD80" s="6" t="inlineStr">
         <is>
           <t>It does not prove any validation rule: every answer on this path is deliberately valid. It does not prove randomization or quota behaviour.</t>
         </is>
       </c>
-      <c r="AE85" s="6" t="inlineStr">
+      <c r="AE80" s="6" t="inlineStr">
         <is>
           <t>Leans on an unconfirmed reading: multi_equality</t>
         </is>
